--- a/visualize/report.xlsx
+++ b/visualize/report.xlsx
@@ -5250,7 +5250,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>Caffeine (cups/day)</t>
+          <t>Caffeine intake (per day, unit not stated)</t>
         </is>
       </c>
       <c r="B55" s="41" t="n">
@@ -7201,7 +7201,7 @@
     <row r="135">
       <c r="A135" s="5" t="inlineStr">
         <is>
-          <t>Caffeine (cups/day)</t>
+          <t>Caffeine intake (per day, unit not stated)</t>
         </is>
       </c>
       <c r="B135" s="41" t="n">
